--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711519</v>
+        <v>113711847</v>
       </c>
       <c r="B2" t="n">
         <v>90131</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713945</v>
+        <v>113715162</v>
       </c>
       <c r="B3" t="n">
-        <v>90149</v>
+        <v>90412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647114</v>
+        <v>646956</v>
       </c>
       <c r="R3" t="n">
-        <v>7037733</v>
+        <v>7037681</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113715162</v>
+        <v>113713945</v>
       </c>
       <c r="B4" t="n">
-        <v>90412</v>
+        <v>90149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646956</v>
+        <v>647114</v>
       </c>
       <c r="R4" t="n">
-        <v>7037681</v>
+        <v>7037733</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711499</v>
+        <v>113711826</v>
       </c>
       <c r="B5" t="n">
         <v>90131</v>

--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711847</v>
+        <v>113711826</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647303</v>
+        <v>647094</v>
       </c>
       <c r="R2" t="n">
-        <v>7037910</v>
+        <v>7037727</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113715162</v>
+        <v>113711847</v>
       </c>
       <c r="B3" t="n">
-        <v>90412</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646956</v>
+        <v>647303</v>
       </c>
       <c r="R3" t="n">
-        <v>7037681</v>
+        <v>7037910</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713945</v>
+        <v>113711808</v>
       </c>
       <c r="B4" t="n">
-        <v>90149</v>
+        <v>90416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647114</v>
+        <v>646956</v>
       </c>
       <c r="R4" t="n">
-        <v>7037733</v>
+        <v>7037681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711826</v>
+        <v>113713945</v>
       </c>
       <c r="B5" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647094</v>
+        <v>647114</v>
       </c>
       <c r="R5" t="n">
-        <v>7037727</v>
+        <v>7037733</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711826</v>
+        <v>113711808</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647094</v>
+        <v>646956</v>
       </c>
       <c r="R2" t="n">
-        <v>7037727</v>
+        <v>7037681</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711847</v>
+        <v>113713964</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711808</v>
+        <v>113711826</v>
       </c>
       <c r="B4" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646956</v>
+        <v>647094</v>
       </c>
       <c r="R4" t="n">
-        <v>7037681</v>
+        <v>7037727</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113713945</v>
+        <v>113711827</v>
       </c>
       <c r="B5" t="n">
         <v>90153</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711808</v>
+        <v>113711827</v>
       </c>
       <c r="B2" t="n">
-        <v>90416</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646956</v>
+        <v>647114</v>
       </c>
       <c r="R2" t="n">
-        <v>7037681</v>
+        <v>7037733</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713964</v>
+        <v>113711826</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647303</v>
+        <v>647094</v>
       </c>
       <c r="R3" t="n">
-        <v>7037910</v>
+        <v>7037727</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711826</v>
+        <v>113711519</v>
       </c>
       <c r="B4" t="n">
         <v>90135</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647094</v>
+        <v>647303</v>
       </c>
       <c r="R4" t="n">
-        <v>7037727</v>
+        <v>7037910</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711827</v>
+        <v>113711808</v>
       </c>
       <c r="B5" t="n">
-        <v>90153</v>
+        <v>90416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647114</v>
+        <v>646956</v>
       </c>
       <c r="R5" t="n">
-        <v>7037733</v>
+        <v>7037681</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711827</v>
+        <v>113711519</v>
       </c>
       <c r="B2" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647114</v>
+        <v>647303</v>
       </c>
       <c r="R2" t="n">
-        <v>7037733</v>
+        <v>7037910</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711826</v>
+        <v>113711500</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647094</v>
+        <v>647114</v>
       </c>
       <c r="R3" t="n">
-        <v>7037727</v>
+        <v>7037733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711519</v>
+        <v>113715162</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647303</v>
+        <v>646956</v>
       </c>
       <c r="R4" t="n">
-        <v>7037910</v>
+        <v>7037681</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711808</v>
+        <v>113711499</v>
       </c>
       <c r="B5" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646956</v>
+        <v>647094</v>
       </c>
       <c r="R5" t="n">
-        <v>7037681</v>
+        <v>7037727</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711519</v>
+        <v>113715162</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647303</v>
+        <v>646956</v>
       </c>
       <c r="R2" t="n">
-        <v>7037910</v>
+        <v>7037681</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711500</v>
+        <v>113713964</v>
       </c>
       <c r="B3" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647114</v>
+        <v>647303</v>
       </c>
       <c r="R3" t="n">
-        <v>7037733</v>
+        <v>7037910</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113715162</v>
+        <v>113713945</v>
       </c>
       <c r="B4" t="n">
-        <v>90416</v>
+        <v>90153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646956</v>
+        <v>647114</v>
       </c>
       <c r="R4" t="n">
-        <v>7037681</v>
+        <v>7037733</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 57585-2023 artfynd.xlsx
+++ b/artfynd/A 57585-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
